--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_ULACIA ZKE.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_ULACIA ZKE.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>154.12</v>
+        <v>375.36</v>
       </c>
       <c r="C2" t="n">
-        <v>154.34</v>
+        <v>373.98</v>
       </c>
       <c r="D2" t="n">
-        <v>101.7234676687832</v>
+        <v>87.17043692176053</v>
       </c>
       <c r="E2" t="n">
-        <v>95.24426590644035</v>
+        <v>93.05310444408794</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4734848484848485</v>
+        <v>0.425</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1773049645390071</v>
+        <v>0.1756547130212611</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3595505617977528</v>
+        <v>0.2957746478873239</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.16875</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="K2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="N2" t="n">
+        <v>55</v>
+      </c>
+      <c r="O2" t="n">
+        <v>113</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.353125</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R2" t="n">
+        <v>45</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.140625</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.16875</v>
+      </c>
+      <c r="Z2" t="n">
         <v>24</v>
       </c>
-      <c r="O2" t="n">
-        <v>51</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.3863636363636364</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>10</v>
-      </c>
-      <c r="R2" t="n">
-        <v>21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.1590909090909091</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.01515151515151515</v>
-      </c>
-      <c r="W2" t="n">
-        <v>6</v>
-      </c>
-      <c r="X2" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.1363636363636364</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13</v>
-      </c>
       <c r="AA2" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3125</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4867256637168141</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.325</v>
+        <v>0.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9734513274336283</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.9827586206896551</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.53125</v>
+        <v>0.3650793650793651</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.647058823529412</v>
+        <v>1.828571428571429</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.8701298701298701</v>
       </c>
       <c r="AO2" t="n">
-        <v>4</v>
+        <v>4.155844155844155</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.96969696969697</v>
+        <v>5.025974025974026</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77.06</v>
+        <v>75.072</v>
       </c>
       <c r="C3" t="n">
-        <v>77.16999999999999</v>
+        <v>74.79599999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>101.7234676687832</v>
+        <v>87.17043692176053</v>
       </c>
       <c r="E3" t="n">
-        <v>95.24426590644035</v>
+        <v>93.05310444408792</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4734848484848485</v>
+        <v>0.425</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1773049645390071</v>
+        <v>0.175654713021261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3595505617977528</v>
+        <v>0.2957746478873239</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2424242424242424</v>
+        <v>0.16875</v>
       </c>
       <c r="J3" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="M3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3863636363636364</v>
+        <v>0.353125</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1590909090909091</v>
+        <v>0.140625</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.025</v>
       </c>
       <c r="W3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1363636363636364</v>
+        <v>0.16875</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
         <v>20</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.303030303030303</v>
+        <v>0.3125</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4867256637168141</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.325</v>
+        <v>0.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9734513274336283</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.9827586206896551</v>
+        <v>0.7792207792207793</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.53125</v>
+        <v>0.3650793650793651</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.647058823529412</v>
+        <v>1.828571428571429</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.8701298701298701</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>4.155844155844155</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.96969696969697</v>
+        <v>5.025974025974026</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>154.56</v>
+        <v>372.6</v>
       </c>
       <c r="C4" t="n">
-        <v>154.34</v>
+        <v>373.98</v>
       </c>
       <c r="D4" t="n">
-        <v>95.24426590644035</v>
+        <v>93.05310444408794</v>
       </c>
       <c r="E4" t="n">
-        <v>101.7234676687832</v>
+        <v>87.17043692176053</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3952702702702703</v>
+        <v>0.3929618768328446</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1148465232825224</v>
+        <v>0.13668430335097</v>
       </c>
       <c r="H4" t="n">
-        <v>0.37</v>
+        <v>0.3584070796460177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2027027027027027</v>
+        <v>0.2346041055718475</v>
       </c>
       <c r="J4" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="M4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N4" t="n">
+        <v>59</v>
+      </c>
+      <c r="O4" t="n">
+        <v>143</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4193548387096774</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>17</v>
+      </c>
+      <c r="R4" t="n">
+        <v>40</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1173020527859238</v>
+      </c>
+      <c r="T4" t="n">
         <v>7</v>
       </c>
-      <c r="N4" t="n">
-        <v>25</v>
-      </c>
-      <c r="O4" t="n">
-        <v>66</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.4459459459459459</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>10</v>
-      </c>
-      <c r="R4" t="n">
-        <v>23</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1554054054054054</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02027027027027027</v>
+        <v>0.05571847507331378</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0472972972972973</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3310810810810811</v>
+        <v>0.313782991202346</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.3787878787878788</v>
+        <v>0.4125874125874126</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.425</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2523364485981308</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.8251748251748252</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.5584415584415584</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.5675675675675675</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.230769230769231</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.090909090909091</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="AO4" t="n">
-        <v>6.727272727272728</v>
+        <v>5.5</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.818181818181818</v>
+        <v>6.435483870967742</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.28</v>
+        <v>74.52000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>77.16999999999999</v>
+        <v>74.79599999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>95.24426590644035</v>
+        <v>93.05310444408792</v>
       </c>
       <c r="E5" t="n">
-        <v>101.7234676687832</v>
+        <v>87.17043692176053</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3952702702702703</v>
+        <v>0.3929618768328446</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1148465232825224</v>
+        <v>0.13668430335097</v>
       </c>
       <c r="H5" t="n">
-        <v>0.37</v>
+        <v>0.3584070796460176</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2027027027027027</v>
+        <v>0.2346041055718475</v>
       </c>
       <c r="J5" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="K5" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>14.5</v>
+        <v>10.8</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="O5" t="n">
-        <v>33</v>
+        <v>28.6</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4459459459459459</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1554054054054054</v>
+        <v>0.1173020527859237</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0.02027027027027027</v>
+        <v>0.05571847507331378</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="X5" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0472972972972973</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="Z5" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>24.5</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3310810810810811</v>
+        <v>0.313782991202346</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.3787878787878788</v>
+        <v>0.4125874125874126</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.425</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2523364485981309</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.8251748251748252</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.7391304347826089</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.3939393939393939</v>
+        <v>0.5584415584415584</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5675675675675675</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.230769230769231</v>
+        <v>2</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.090909090909091</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="AO5" t="n">
-        <v>6.727272727272728</v>
+        <v>5.5</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.818181818181818</v>
+        <v>6.435483870967741</v>
       </c>
     </row>
     <row r="7">
@@ -1429,40 +1429,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1477,19 +1477,19 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
@@ -1510,60 +1510,60 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>04:51</t>
+          <t>35:26</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>10.88</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1</v>
+        <v>0.551</v>
       </c>
       <c r="AR8" t="n">
-        <v>2</v>
+        <v>1.103</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -1575,13 +1575,13 @@
         <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.094</v>
+        <v>0.144</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.197</v>
+        <v>0.109</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="BA8" t="n">
         <v>0</v>
@@ -1594,91 +1594,91 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" t="n">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
-        <v>14</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
+        <v>39</v>
+      </c>
+      <c r="L9" t="n">
+        <v>18</v>
+      </c>
+      <c r="M9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>19</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4</v>
-      </c>
       <c r="N9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>71</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6</v>
+      </c>
+      <c r="X9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>43</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1</v>
-      </c>
       <c r="Y9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.667</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1709,47 +1709,47 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>63:55</t>
+          <t>136:53</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>17.64</v>
+        <v>42.48</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.643</v>
+        <v>0.536</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.601</v>
+        <v>0.479</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.134</v>
+        <v>0.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.057</v>
+        <v>0.165</v>
       </c>
       <c r="AT9" t="n">
         <v>0.143</v>
       </c>
       <c r="AU9" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AV9" t="n">
         <v>4</v>
       </c>
-      <c r="AV9" t="n">
-        <v>14</v>
-      </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>5.286</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.126</v>
+        <v>0.145</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.149</v>
+        <v>0.127</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.253</v>
+        <v>0.258</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="10">
@@ -1759,162 +1759,162 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" t="n">
+        <v>15</v>
+      </c>
+      <c r="G10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H10" t="n">
         <v>16</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>16</v>
+      </c>
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="G10" t="n">
+      <c r="M10" t="n">
+        <v>5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
         <v>16</v>
       </c>
-      <c r="H10" t="n">
-        <v>5</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>11</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>37</v>
+      </c>
+      <c r="U10" t="n">
         <v>9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>9</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3</v>
       </c>
       <c r="V10" t="n">
         <v>3</v>
       </c>
       <c r="W10" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="X10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH10" t="n">
         <v>5</v>
       </c>
-      <c r="Y10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
       <c r="AI10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.25</v>
+        <v>0.455</v>
       </c>
       <c r="AK10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AL10" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.333</v>
+        <v>0.303</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>60:12</t>
+          <t>143:06</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>43.96</v>
+        <v>105.56</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.422</v>
+        <v>0.449</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.445</v>
+        <v>0.486</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.728</v>
+        <v>0.824</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.182</v>
+        <v>0.152</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.156</v>
+        <v>0.203</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>4.938</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.125</v>
+        <v>5.812</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.214</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="11">
@@ -1924,61 +1924,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6</v>
+      </c>
+      <c r="I11" t="n">
         <v>9</v>
       </c>
-      <c r="F11" t="n">
+      <c r="J11" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="P11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1987,43 +1987,43 @@
         <v>5</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
         <v>2</v>
       </c>
       <c r="Z11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
         <v>7</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
         <v>0.286</v>
       </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AJ11" t="n">
         <v>0.4</v>
@@ -2032,54 +2032,54 @@
         <v>2</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>61:31</t>
+          <t>131:12</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>25.08</v>
+        <v>49.96</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.4</v>
+        <v>0.368</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.433</v>
+        <v>0.405</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.797</v>
+        <v>0.681</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.2</v>
+        <v>0.158</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>6.25</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.186</v>
+        <v>0.178</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.041</v>
+        <v>0.055</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="12">
@@ -2089,82 +2089,82 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F12" t="n">
+        <v>9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" t="n">
         <v>5</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
         <v>13</v>
       </c>
-      <c r="H12" t="n">
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>20</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>8</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>8</v>
-      </c>
-      <c r="X12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2179,72 +2179,72 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AK12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.556</v>
+        <v>0.467</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>51:30</t>
+          <t>122:18</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>18.76</v>
+        <v>39.2</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.536</v>
+        <v>0.484</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.603</v>
+        <v>0.526</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.013</v>
+        <v>0.918</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.16</v>
+        <v>0.128</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.286</v>
+        <v>0.156</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.667</v>
+        <v>6.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.333</v>
+        <v>6.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.166</v>
+        <v>0.15</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.066</v>
+        <v>0.096</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.042</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="13">
@@ -2400,16 +2400,16 @@
         <v>2.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.212</v>
+        <v>0.217</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.041</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="14">
@@ -2419,162 +2419,162 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13</v>
+      </c>
+      <c r="I14" t="n">
+        <v>19</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>22</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>12</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>46</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
+      </c>
+      <c r="V14" t="n">
         <v>9</v>
       </c>
-      <c r="E14" t="n">
-        <v>19</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>9</v>
       </c>
-      <c r="I14" t="n">
-        <v>12</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3</v>
-      </c>
-      <c r="K14" t="n">
-        <v>12</v>
-      </c>
-      <c r="L14" t="n">
-        <v>8</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
+      <c r="Z14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
         <v>5</v>
       </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>34</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>5</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AK14" t="n">
         <v>1</v>
       </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.25</v>
+        <v>0.143</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>55:40</t>
+          <t>117:05</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>33.28</v>
+        <v>63.36</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.48</v>
+        <v>0.404</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.545</v>
+        <v>0.461</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.992</v>
+        <v>0.805</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.09</v>
+        <v>0.126</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.36</v>
+        <v>0.277</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.333</v>
+        <v>5.875</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.333</v>
+        <v>6.625</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.273</v>
+        <v>0.253</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.137</v>
+        <v>0.115</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.183</v>
+        <v>0.17</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="15">
@@ -2584,61 +2584,61 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D15" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
         <v>4</v>
       </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="L15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2647,28 +2647,28 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.333</v>
+        <v>0.538</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2692,54 +2692,54 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>24:06</t>
+          <t>76:26</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>7</v>
+        <v>27.2</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.4</v>
+        <v>0.524</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.4</v>
+        <v>0.496</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.571</v>
+        <v>0.846</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.286</v>
+        <v>0.147</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="AW15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.133</v>
+        <v>0.166</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.119</v>
+        <v>0.063</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="16">
@@ -2749,22 +2749,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H16" t="n">
         <v>3</v>
@@ -2773,13 +2773,13 @@
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
@@ -2788,22 +2788,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2848,63 +2848,63 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.222</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>55:31</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>4.76</v>
+        <v>22.76</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.75</v>
+        <v>0.231</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.798</v>
+        <v>0.305</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.261</v>
+        <v>0.395</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.21</v>
+        <v>0.351</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>0.231</v>
       </c>
       <c r="AU16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>1.625</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>2.625</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.114</v>
+        <v>0.192</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.096</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2914,89 +2914,89 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
+        <v>16</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>21</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>4</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
         <v>3</v>
       </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
@@ -3004,72 +3004,72 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1</v>
+        <v>0.286</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>26:38</t>
+          <t>80:33</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.25</v>
+        <v>0.258</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.25</v>
+        <v>0.258</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.3</v>
+        <v>0.432</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.4</v>
+        <v>0.162</v>
       </c>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.5</v>
+        <v>5.167</v>
       </c>
       <c r="AW17" t="n">
-        <v>2</v>
+        <v>6.667</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.171</v>
+        <v>0.215</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.128</v>
+        <v>0.101</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.038</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="18">
@@ -3079,40 +3079,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3121,19 +3121,19 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3142,19 +3142,19 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
@@ -3187,54 +3187,54 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>42:39</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>10.44</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -3390,7 +3390,7 @@
         <v>2</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.255</v>
+        <v>0.261</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -3409,40 +3409,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3451,120 +3451,120 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
+        <v>9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>37:17</t>
+        </is>
+      </c>
+      <c r="AO20" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW20" t="n">
         <v>3</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.327</v>
+        <v>0.219</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3574,7 +3574,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -3601,10 +3601,10 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -3616,10 +3616,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -3739,159 +3739,159 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
-        <v>157</v>
+        <v>326</v>
       </c>
       <c r="D22" t="n">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>166</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="H22" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I22" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="J22" t="n">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="K22" t="n">
+        <v>145</v>
+      </c>
+      <c r="L22" t="n">
         <v>63</v>
       </c>
-      <c r="L22" t="n">
-        <v>32</v>
-      </c>
       <c r="M22" t="n">
+        <v>37</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13</v>
+      </c>
+      <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>4</v>
-      </c>
       <c r="P22" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="Q22" t="n">
+        <v>35</v>
+      </c>
+      <c r="R22" t="n">
+        <v>110</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>186</v>
+      </c>
+      <c r="U22" t="n">
         <v>20</v>
       </c>
-      <c r="R22" t="n">
-        <v>51</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>108</v>
-      </c>
-      <c r="U22" t="n">
-        <v>11</v>
-      </c>
       <c r="V22" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="W22" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="Y22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>113</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>45</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>54</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="AK22" t="n">
         <v>24</v>
       </c>
-      <c r="Z22" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.476</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>13</v>
-      </c>
       <c r="AL22" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.325</v>
+        <v>0.24</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>425:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>186.12</v>
+        <v>438.36</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.473</v>
+        <v>0.425</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.513</v>
+        <v>0.451</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.844</v>
+        <v>0.744</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.242</v>
+        <v>0.169</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="AV22" t="n">
-        <v>4</v>
+        <v>4.156</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.97</v>
+        <v>5.026</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.059</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3904,159 +3904,159 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C23" t="n">
-        <v>147</v>
+        <v>348</v>
       </c>
       <c r="D23" t="n">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="E23" t="n">
-        <v>92</v>
+        <v>203</v>
       </c>
       <c r="F23" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="G23" t="n">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="H23" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="I23" t="n">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="J23" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="K23" t="n">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="M23" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="N23" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="Q23" t="n">
+        <v>25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>105</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>235</v>
+      </c>
+      <c r="U23" t="n">
+        <v>43</v>
+      </c>
+      <c r="V23" t="n">
+        <v>34</v>
+      </c>
+      <c r="W23" t="n">
+        <v>54</v>
+      </c>
+      <c r="X23" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>143</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AE23" t="n">
         <v>7</v>
       </c>
-      <c r="R23" t="n">
-        <v>50</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>77</v>
-      </c>
-      <c r="U23" t="n">
-        <v>13</v>
-      </c>
-      <c r="V23" t="n">
-        <v>21</v>
-      </c>
-      <c r="W23" t="n">
-        <v>29</v>
-      </c>
-      <c r="X23" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>66</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
       <c r="AF23" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AG23" t="n">
-        <v>0.333</v>
+        <v>0.368</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AI23" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.143</v>
+        <v>0.226</v>
       </c>
       <c r="AK23" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="AL23" t="n">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.286</v>
+        <v>0.252</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>425:00</t>
+          <t>1025:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>191.56</v>
+        <v>453.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.395</v>
+        <v>0.393</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.433</v>
+        <v>0.444</v>
       </c>
       <c r="AR23" t="n">
         <v>0.767</v>
       </c>
       <c r="AS23" t="n">
-        <v>0.115</v>
+        <v>0.137</v>
       </c>
       <c r="AT23" t="n">
-        <v>0.203</v>
+        <v>0.235</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.091</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AV23" t="n">
-        <v>6.727</v>
+        <v>5.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.818</v>
+        <v>6.435</v>
       </c>
       <c r="AX23" t="n">
         <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.074</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.128</v>
+        <v>0.141</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4128,141 +4128,141 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="D25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0</v>
-      </c>
       <c r="AK25" t="n">
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AM25" t="n">
         <v>0</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>02:25</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>0.5</v>
+        <v>2.176</v>
       </c>
       <c r="AP25" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1</v>
+        <v>0.551</v>
       </c>
       <c r="AR25" t="n">
-        <v>2</v>
+        <v>1.103</v>
       </c>
       <c r="AS25" t="n">
         <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
@@ -4274,13 +4274,13 @@
         <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.094</v>
+        <v>0.144</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.197</v>
+        <v>0.109</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="BA25" t="n">
         <v>0</v>
@@ -4293,16 +4293,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="D26" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4311,73 +4311,73 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K26" t="n">
-        <v>9.5</v>
+        <v>7.8</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="N26" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R26" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.667</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AC26" t="n">
         <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AE26" t="n">
         <v>0</v>
@@ -4408,47 +4408,47 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>31:57</t>
+          <t>27:22</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>8.82</v>
+        <v>8.496</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.643</v>
+        <v>0.536</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.601</v>
+        <v>0.479</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.134</v>
+        <v>0.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.057</v>
+        <v>0.165</v>
       </c>
       <c r="AT26" t="n">
         <v>0.143</v>
       </c>
       <c r="AU26" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="AV26" t="n">
         <v>4</v>
       </c>
-      <c r="AV26" t="n">
-        <v>14</v>
-      </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>5.286</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.126</v>
+        <v>0.145</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.149</v>
+        <v>0.127</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.253</v>
+        <v>0.258</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="27">
@@ -4458,162 +4458,162 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="D27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7</v>
+      </c>
+      <c r="F27" t="n">
         <v>3</v>
       </c>
-      <c r="E27" t="n">
-        <v>8</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="G27" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>37</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG27" t="n">
         <v>0.5</v>
       </c>
-      <c r="M27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>9</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
       <c r="AH27" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0.25</v>
+        <v>0.455</v>
       </c>
       <c r="AK27" t="n">
         <v>2</v>
       </c>
       <c r="AL27" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.333</v>
+        <v>0.303</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>30:06</t>
+          <t>28:37</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>21.98</v>
+        <v>21.112</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.422</v>
+        <v>0.449</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.445</v>
+        <v>0.486</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.728</v>
+        <v>0.824</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.182</v>
+        <v>0.152</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.156</v>
+        <v>0.203</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.125</v>
+        <v>0.875</v>
       </c>
       <c r="AV27" t="n">
-        <v>4</v>
+        <v>4.938</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.125</v>
+        <v>5.812</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.333</v>
+        <v>0.345</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.016</v>
+        <v>0.034</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.101</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.214</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="28">
@@ -4623,162 +4623,162 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="D28" t="n">
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="F28" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
-        <v>5.5</v>
+        <v>4.4</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="K28" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="M28" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD28" t="n">
         <v>0.286</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AJ28" t="n">
         <v>0.4</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AL28" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>30:45</t>
+          <t>26:14</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>12.54</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.4</v>
+        <v>0.368</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.433</v>
+        <v>0.405</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.797</v>
+        <v>0.681</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="AT28" t="n">
-        <v>0.2</v>
+        <v>0.158</v>
       </c>
       <c r="AU28" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="AW28" t="n">
-        <v>12</v>
+        <v>6.25</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.186</v>
+        <v>0.178</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.016</v>
+        <v>0.007</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.041</v>
+        <v>0.055</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.114</v>
       </c>
     </row>
     <row r="29">
@@ -4788,162 +4788,162 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>20</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AA29" t="n">
         <v>0.5</v>
       </c>
-      <c r="F29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL29" t="n">
         <v>3</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>8</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>4</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AM29" t="n">
-        <v>0.556</v>
+        <v>0.467</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>25:45</t>
+          <t>24:27</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>9.380000000000001</v>
+        <v>7.84</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.536</v>
+        <v>0.484</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.603</v>
+        <v>0.526</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.013</v>
+        <v>0.918</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.16</v>
+        <v>0.128</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.286</v>
+        <v>0.156</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.667</v>
+        <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.333</v>
+        <v>6.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.166</v>
+        <v>0.15</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.066</v>
+        <v>0.096</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.042</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="30">
@@ -5099,16 +5099,16 @@
         <v>2.2</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.212</v>
+        <v>0.217</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.024</v>
+        <v>0.025</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.041</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="31">
@@ -5118,67 +5118,67 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>16.5</v>
+        <v>10.2</v>
       </c>
       <c r="D31" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="E31" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="J31" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="R31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V31" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -5187,93 +5187,93 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.308</v>
+        <v>0.375</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.833</v>
+        <v>0.7</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AI31" t="n">
         <v>1</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AK31" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AL31" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.25</v>
+        <v>0.143</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>27:50</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>16.64</v>
+        <v>12.672</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.48</v>
+        <v>0.404</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.545</v>
+        <v>0.461</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.992</v>
+        <v>0.805</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.09</v>
+        <v>0.126</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.36</v>
+        <v>0.277</v>
       </c>
       <c r="AU31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV31" t="n">
-        <v>8.333</v>
+        <v>5.875</v>
       </c>
       <c r="AW31" t="n">
-        <v>9.333</v>
+        <v>6.625</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.273</v>
+        <v>0.253</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.137</v>
+        <v>0.115</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.183</v>
+        <v>0.17</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="32">
@@ -5283,61 +5283,61 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="E32" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -5346,28 +5346,28 @@
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.333</v>
+        <v>0.538</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -5391,54 +5391,54 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AM32" t="n">
         <v>0</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>3.5</v>
+        <v>5.44</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.4</v>
+        <v>0.524</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.4</v>
+        <v>0.496</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.571</v>
+        <v>0.846</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.286</v>
+        <v>0.147</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AU32" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.5</v>
+        <v>5.25</v>
       </c>
       <c r="AW32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.133</v>
+        <v>0.166</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.119</v>
+        <v>0.063</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>0.047</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.02</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="33">
@@ -5448,61 +5448,61 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="H33" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J33" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M33" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>8</v>
+        <v>-3</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5511,16 +5511,16 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="X33" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="Y33" t="n">
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -5547,63 +5547,63 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AL33" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.5</v>
+        <v>0.222</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>2.38</v>
+        <v>4.552</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.75</v>
+        <v>0.231</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.798</v>
+        <v>0.305</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.261</v>
+        <v>0.395</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.21</v>
+        <v>0.351</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.5</v>
+        <v>0.231</v>
       </c>
       <c r="AU33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV33" t="n">
-        <v>2</v>
+        <v>1.625</v>
       </c>
       <c r="AW33" t="n">
-        <v>7</v>
+        <v>2.625</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.114</v>
+        <v>0.192</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.089</v>
+        <v>0.098</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.096</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -5613,162 +5613,162 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
         <v>1.5</v>
       </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AV34" t="n">
-        <v>1.5</v>
+        <v>5.167</v>
       </c>
       <c r="AW34" t="n">
-        <v>2</v>
+        <v>6.667</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.171</v>
+        <v>0.215</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.036</v>
+        <v>0.012</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.128</v>
+        <v>0.101</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.038</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="35">
@@ -5778,40 +5778,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5820,19 +5820,19 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -5841,19 +5841,19 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -5886,54 +5886,54 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AM35" t="n">
         <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>00:36</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.311</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.383</v>
       </c>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="36">
@@ -6089,7 +6089,7 @@
         <v>2</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.255</v>
+        <v>0.261</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
@@ -6108,40 +6108,40 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -6150,120 +6150,120 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW37" t="n">
         <v>3</v>
       </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0</v>
-      </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.327</v>
+        <v>0.219</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="38">
@@ -6273,7 +6273,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -6300,10 +6300,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="L38" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -6315,10 +6315,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -6438,159 +6438,159 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>78.5</v>
+        <v>65.2</v>
       </c>
       <c r="D39" t="n">
-        <v>17</v>
+        <v>15.2</v>
       </c>
       <c r="E39" t="n">
-        <v>37</v>
+        <v>33.2</v>
       </c>
       <c r="F39" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I39" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K39" t="n">
         <v>29</v>
       </c>
-      <c r="H39" t="n">
-        <v>16</v>
-      </c>
-      <c r="I39" t="n">
-        <v>24</v>
-      </c>
-      <c r="J39" t="n">
-        <v>16</v>
-      </c>
-      <c r="K39" t="n">
-        <v>31.5</v>
-      </c>
       <c r="L39" t="n">
-        <v>16</v>
+        <v>12.6</v>
       </c>
       <c r="M39" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
+        <v>15</v>
+      </c>
+      <c r="P39" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>22</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>186</v>
+      </c>
+      <c r="U39" t="n">
         <v>4</v>
       </c>
-      <c r="P39" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>10</v>
-      </c>
-      <c r="R39" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>108</v>
-      </c>
-      <c r="U39" t="n">
-        <v>5.5</v>
-      </c>
       <c r="V39" t="n">
-        <v>8.5</v>
+        <v>4.6</v>
       </c>
       <c r="W39" t="n">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="X39" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Y39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
-        <v>25.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.471</v>
+        <v>0.487</v>
       </c>
       <c r="AB39" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AC39" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.476</v>
+        <v>0.4</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AF39" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AH39" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>9</v>
+        <v>10.8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.333</v>
+        <v>0.296</v>
       </c>
       <c r="AK39" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="AL39" t="n">
         <v>20</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.325</v>
+        <v>0.24</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>212:30</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>93.06</v>
+        <v>87.672</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.473</v>
+        <v>0.425</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.513</v>
+        <v>0.451</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.844</v>
+        <v>0.744</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.242</v>
+        <v>0.169</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="AV39" t="n">
-        <v>4</v>
+        <v>4.156</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.97</v>
+        <v>5.026</v>
       </c>
       <c r="AX39" t="n">
         <v>0.2</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.059</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.126</v>
+        <v>0.128</v>
       </c>
       <c r="BA39" t="n">
         <v>0</v>
@@ -6603,159 +6603,159 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>73.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>18</v>
+        <v>16.6</v>
       </c>
       <c r="E40" t="n">
-        <v>46</v>
+        <v>40.6</v>
       </c>
       <c r="F40" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="G40" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="H40" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="K40" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="L40" t="n">
-        <v>18.5</v>
+        <v>16.2</v>
       </c>
       <c r="M40" t="n">
-        <v>6.5</v>
+        <v>8.4</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O40" t="n">
+        <v>14</v>
+      </c>
+      <c r="P40" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Q40" t="n">
         <v>5</v>
       </c>
-      <c r="P40" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R40" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="U40" t="n">
-        <v>6.5</v>
+        <v>8.6</v>
       </c>
       <c r="V40" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="W40" t="n">
-        <v>14.5</v>
+        <v>10.8</v>
       </c>
       <c r="X40" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>33</v>
+        <v>28.6</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.379</v>
+        <v>0.413</v>
       </c>
       <c r="AB40" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AC40" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.435</v>
+        <v>0.425</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.333</v>
+        <v>0.368</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="AI40" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.143</v>
+        <v>0.226</v>
       </c>
       <c r="AK40" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AL40" t="n">
-        <v>24.5</v>
+        <v>21.4</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.286</v>
+        <v>0.252</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>212:30</t>
+          <t>205:00</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>95.78</v>
+        <v>90.72</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.395</v>
+        <v>0.393</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.433</v>
+        <v>0.444</v>
       </c>
       <c r="AR40" t="n">
         <v>0.767</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.115</v>
+        <v>0.137</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.203</v>
+        <v>0.235</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.091</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AV40" t="n">
-        <v>6.727</v>
+        <v>5.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.818</v>
+        <v>6.435</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.206</v>
+        <v>0.207</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.083</v>
+        <v>0.076</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.114</v>
+        <v>0.133</v>
       </c>
       <c r="BA40" t="n">
         <v>0</v>
